--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -24,8 +24,11 @@
     <sheet name="SERIES" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="CLUBS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="META" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -33,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +51,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,12 +96,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21541,7 +21559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21634,6 +21652,71 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1993_94_0030 'I.ČLTK Praha' prev→CLUB_S1992_93_0066 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1993_94_0168 'Třeboň B' prev→CLUB_S1992_93_0215 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1993_94_0285 'Úpice B' prev→CLUB_S1992_93_0366 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1993_94_0361 'Růžená B' prev→CLUB_S1992_93_0396 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0020</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1993_94_0020 'Baráž o Extraligu' (L15, parent=NODE_S1993_94_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -25676,8 +25759,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -25757,7 +25838,6 @@
         </is>
       </c>
     </row>
-    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
@@ -47785,6 +47865,171 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0030</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0030 'I.ČLTK Praha' prev→CLUB_S1992_93_0066 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0168</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0168 'Třeboň B' prev→CLUB_S1992_93_0215 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0285</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0285 'Úpice B' prev→CLUB_S1992_93_0366 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0361</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0361 'Růžená B' prev→CLUB_S1992_93_0396 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0020</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1993_94_0020 'Baráž o Extraligu' (L15, parent=NODE_S1993_94_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21559,7 +21559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21658,7 +21658,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1993_94_0030 'I.ČLTK Praha' prev→CLUB_S1992_93_0066 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -21670,7 +21670,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1993_94_0168 'Třeboň B' prev→CLUB_S1992_93_0215 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -21682,7 +21682,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1993_94_0285 'Úpice B' prev→CLUB_S1992_93_0366 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -21694,7 +21694,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1993_94_0361 'Růžená B' prev→CLUB_S1992_93_0396 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -21704,17 +21704,420 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NODE_S1993_94_0020</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1993_94_0020 'Baráž o Extraligu' (L15, parent=NODE_S1993_94_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0066 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Mariánské Lázně' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0161 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0215 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0366 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0396 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0508 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0475 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0476 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -25759,6 +26162,8 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -25789,6 +26194,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0001</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -25801,6 +26211,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0003</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -25813,6 +26228,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0003</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -25825,6 +26245,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0031</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -25838,6 +26263,7 @@
         </is>
       </c>
     </row>
+    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
@@ -28378,12 +28804,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -28761,12 +29187,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -28808,12 +29234,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -28976,12 +29402,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -29023,12 +29449,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -29065,12 +29491,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -29890,12 +30316,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -29974,12 +30400,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -30325,12 +30751,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Mariánské Lázně' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Mariánské Lázně</t>
         </is>
       </c>
     </row>
@@ -30923,12 +31349,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -34041,12 +34467,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -34125,12 +34551,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -35166,12 +35592,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -35396,12 +35822,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -35443,12 +35869,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -35537,12 +35963,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -36343,12 +36769,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -38190,12 +38616,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -38284,12 +38710,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou. || TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Bižuterie Jablonec</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -38447,12 +38873,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -39287,12 +39713,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -41764,12 +42190,12 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -46866,12 +47292,12 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -47875,11 +48301,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -47924,21 +48350,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0030</t>
+          <t>CLUB_S1993_94_0002</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0030 'I.ČLTK Praha' prev→CLUB_S1992_93_0066 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -47946,21 +48370,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0168</t>
+          <t>CLUB_S1993_94_0011</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0168 'Třeboň B' prev→CLUB_S1992_93_0215 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -47968,21 +48390,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0285</t>
+          <t>CLUB_S1993_94_0012</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0285 'Úpice B' prev→CLUB_S1992_93_0366 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -47990,21 +48410,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0361</t>
+          <t>CLUB_S1993_94_0018</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0361 'Růžená B' prev→CLUB_S1992_93_0396 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -48012,24 +48430,702 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1993_94_0020</t>
+          <t>CLUB_S1993_94_0019</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1993_94_0020 'Baráž o Extraligu' (L15, parent=NODE_S1993_94_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0020</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0030</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0066 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0040</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0042</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0050</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Mariánské Lázně' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0053</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0064</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0083</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0161 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0133</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0135</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0135</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0158</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0163</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0164</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0166</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0168</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0215 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0184</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0225</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0227</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0231</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0237</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0251</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0254</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0282</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0285</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0366 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0294</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0307</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0310</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0314</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0361</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0396 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0365</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0508 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0400</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0475 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0404</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0476 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1993_94_0425</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21559,7 +21559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21658,7 +21658,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -21670,7 +21670,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -21682,7 +21682,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -21694,7 +21694,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0066 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -21706,7 +21706,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -21718,7 +21718,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -21730,7 +21730,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0066 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -21742,7 +21742,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0161 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -21754,7 +21754,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -21766,7 +21766,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Mariánské Lázně' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -21778,7 +21778,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -21790,7 +21790,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -21802,7 +21802,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0161 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0215 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -21814,7 +21814,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -21826,7 +21826,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -21838,7 +21838,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -21850,7 +21850,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -21862,7 +21862,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -21874,7 +21874,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -21886,7 +21886,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -21898,7 +21898,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0215 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -21910,7 +21910,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0366 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -21922,7 +21922,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -21934,7 +21934,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -21946,7 +21946,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -21958,7 +21958,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -21970,7 +21970,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0396 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -21982,7 +21982,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0508 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -21994,7 +21994,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0475 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -22006,118 +22006,10 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0366 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0476 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0396 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0508 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0475 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0476 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -22134,7 +22026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22193,6 +22085,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22282,6 +22179,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22366,6 +22268,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0006</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22408,6 +22315,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0007</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22450,6 +22362,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0008</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22492,6 +22409,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0009</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22534,6 +22456,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0010</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22576,6 +22503,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0011</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22618,6 +22550,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0012</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22660,6 +22597,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0013</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22702,6 +22644,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0014</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22744,6 +22691,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0015</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22786,6 +22738,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0016</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22828,6 +22785,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0017</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22870,6 +22832,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0018</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -22912,6 +22879,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0019</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22954,6 +22926,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0020</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -23342,6 +23319,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0030</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -23683,6 +23665,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0058</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -23725,6 +23712,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0059</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -23809,6 +23801,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0060</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -23851,6 +23848,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0061</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -23893,6 +23895,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0062</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -23977,6 +23984,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0064</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -24019,6 +24031,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0065</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -24061,6 +24078,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0066</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -24103,6 +24125,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0067</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -24145,6 +24172,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0068</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -24313,6 +24345,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0073</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -24355,6 +24392,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0074</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -24439,6 +24481,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0075</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -24481,6 +24528,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0076</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -24607,6 +24659,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0080</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -24649,6 +24706,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0081</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -24691,6 +24753,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0082</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -24733,6 +24800,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0083</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -24775,6 +24847,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0084</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -24817,6 +24894,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0085</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -25027,6 +25109,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0095</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -25069,6 +25156,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0096</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -25321,6 +25413,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0104</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -25363,6 +25460,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0105</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -25405,6 +25507,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0106</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -25447,6 +25554,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0107</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -25489,6 +25601,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0108</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -25531,6 +25648,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0109</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -25741,6 +25863,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0113</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -25783,6 +25910,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0114</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -26035,6 +26167,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0116</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -26075,6 +26212,11 @@
       <c r="J93" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0117</t>
         </is>
       </c>
     </row>
@@ -28804,12 +28946,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -29187,12 +29329,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -29402,12 +29544,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -30316,12 +30458,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -30751,12 +30893,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Mariánské Lázně' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Mariánské Lázně</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -34467,12 +34609,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -34551,12 +34693,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -35822,12 +35964,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -47292,12 +47434,12 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -48301,7 +48443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -48355,12 +48497,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0002</t>
+          <t>CLUB_S1993_94_0012</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48375,12 +48517,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0011</t>
+          <t>CLUB_S1993_94_0019</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48395,12 +48537,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0012</t>
+          <t>CLUB_S1993_94_0020</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48415,12 +48557,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0018</t>
+          <t>CLUB_S1993_94_0030</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0066 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -48435,12 +48577,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0019</t>
+          <t>CLUB_S1993_94_0042</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48455,12 +48597,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0020</t>
+          <t>CLUB_S1993_94_0053</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -48475,12 +48617,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0030</t>
+          <t>CLUB_S1993_94_0064</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0066 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48495,12 +48637,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0040</t>
+          <t>CLUB_S1993_94_0083</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0161 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -48515,12 +48657,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0042</t>
+          <t>CLUB_S1993_94_0135</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48535,12 +48677,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0050</t>
+          <t>CLUB_S1993_94_0158</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Mariánské Lázně' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48555,12 +48697,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0053</t>
+          <t>CLUB_S1993_94_0164</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48575,12 +48717,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0064</t>
+          <t>CLUB_S1993_94_0166</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48595,12 +48737,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0083</t>
+          <t>CLUB_S1993_94_0168</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0161 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0215 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -48615,12 +48757,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0133</t>
+          <t>CLUB_S1993_94_0184</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48635,12 +48777,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0135</t>
+          <t>CLUB_S1993_94_0225</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48655,12 +48797,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0135</t>
+          <t>CLUB_S1993_94_0227</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48675,12 +48817,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0158</t>
+          <t>CLUB_S1993_94_0231</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48695,12 +48837,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0163</t>
+          <t>CLUB_S1993_94_0237</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -48715,12 +48857,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0164</t>
+          <t>CLUB_S1993_94_0251</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48735,12 +48877,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0166</t>
+          <t>CLUB_S1993_94_0254</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -48755,12 +48897,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0168</t>
+          <t>CLUB_S1993_94_0282</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0215 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -48775,12 +48917,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0184</t>
+          <t>CLUB_S1993_94_0285</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0366 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -48795,12 +48937,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0225</t>
+          <t>CLUB_S1993_94_0294</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -48815,12 +48957,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0227</t>
+          <t>CLUB_S1993_94_0307</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48835,12 +48977,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0231</t>
+          <t>CLUB_S1993_94_0310</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -48855,12 +48997,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0237</t>
+          <t>CLUB_S1993_94_0314</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -48875,12 +49017,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0251</t>
+          <t>CLUB_S1993_94_0361</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0396 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -48895,12 +49037,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0254</t>
+          <t>CLUB_S1993_94_0365</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0508 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -48915,12 +49057,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0282</t>
+          <t>CLUB_S1993_94_0400</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0475 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -48935,197 +49077,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1993_94_0285</t>
+          <t>CLUB_S1993_94_0404</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0366 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0294</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0307</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0310</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0314</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0361</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0396 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0365</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0508 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0400</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0475 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0404</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0476 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0425</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F40"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21559,7 +21559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22010,6 +22010,54 @@
         </is>
       </c>
       <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -48443,7 +48491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -49086,8 +49134,88 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AC ZPS Zlín</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HC Olomouc</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HC Chemopetrol Litvínov</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>HC Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F31"/>
+  <autoFilter ref="A1:F35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -760,13 +760,13 @@
         <v>24</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>182</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -774,7 +774,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>182</v>
+        <v>151</v>
+      </c>
+      <c r="M5" t="n">
+        <v>56</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -835,13 +838,13 @@
         <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -849,7 +852,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>163</v>
+        <v>120</v>
+      </c>
+      <c r="M6" t="n">
+        <v>52</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -910,13 +916,13 @@
         <v>19</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>162</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -924,7 +930,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>162</v>
+        <v>138</v>
+      </c>
+      <c r="M7" t="n">
+        <v>49</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -982,16 +991,16 @@
         <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -999,7 +1008,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>154</v>
+        <v>163</v>
+      </c>
+      <c r="M8" t="n">
+        <v>49</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1060,13 +1072,13 @@
         <v>21</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>162</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1074,7 +1086,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>162</v>
+        <v>129</v>
+      </c>
+      <c r="M9" t="n">
+        <v>48</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1135,13 +1150,13 @@
         <v>22</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>142</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1149,7 +1164,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>142</v>
+        <v>128</v>
+      </c>
+      <c r="M10" t="n">
+        <v>48</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1207,16 +1225,16 @@
         <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1224,7 +1242,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>116</v>
+        <v>123</v>
+      </c>
+      <c r="M11" t="n">
+        <v>45</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1282,16 +1303,16 @@
         <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1299,7 +1320,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>161</v>
+        <v>154</v>
+      </c>
+      <c r="M12" t="n">
+        <v>44</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1357,16 +1381,16 @@
         <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1374,7 +1398,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>132</v>
+        <v>140</v>
+      </c>
+      <c r="M13" t="n">
+        <v>38</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1435,13 +1462,13 @@
         <v>16</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1449,7 +1476,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>131</v>
+        <v>143</v>
+      </c>
+      <c r="M14" t="n">
+        <v>38</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1515,13 +1545,13 @@
         <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,7 +1559,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>133</v>
+        <v>163</v>
+      </c>
+      <c r="M15" t="n">
+        <v>35</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1592,16 +1625,16 @@
         <v>44</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1609,7 +1642,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>107</v>
+        <v>193</v>
+      </c>
+      <c r="M16" t="n">
+        <v>26</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2221,13 +2257,19 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
+      <c r="J33" t="n">
+        <v>29</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>29</v>
+        <v>13</v>
+      </c>
+      <c r="M33" t="n">
+        <v>10</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2293,6 +2335,9 @@
       <c r="I34" t="n">
         <v>2</v>
       </c>
+      <c r="J34" t="n">
+        <v>21</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>:</t>
@@ -2301,6 +2346,9 @@
       <c r="L34" t="n">
         <v>21</v>
       </c>
+      <c r="M34" t="n">
+        <v>7</v>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>Extraliga / finále / O baráž / Baráž o Extraligu</t>
@@ -2365,13 +2413,19 @@
       <c r="I35" t="n">
         <v>3</v>
       </c>
+      <c r="J35" t="n">
+        <v>17</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2437,13 +2491,19 @@
       <c r="I36" t="n">
         <v>4</v>
       </c>
+      <c r="J36" t="n">
+        <v>17</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -21559,7 +21619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22010,54 +22070,6 @@
         </is>
       </c>
       <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -48491,7 +48503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -49134,88 +49146,8 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AC ZPS Zlín</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>HC Olomouc</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>HC Chemopetrol Litvínov</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>HC Dukla Jihlava</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F35"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -22086,7 +22086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22150,6 +22150,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26364,8 +26374,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -26465,7 +26473,6 @@
         </is>
       </c>
     </row>
-    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>

--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -22328,6 +22328,16 @@
           <t>NODE_S1993_94_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0009</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0015</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22342,6 +22352,14 @@
         <is>
           <t>NODE_S1992_93_0006</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -22516,6 +22534,16 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0009</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0018</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22530,6 +22558,14 @@
         <is>
           <t>NODE_S1992_93_0010</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -22563,6 +22599,16 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0010</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0018</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22577,6 +22623,14 @@
         <is>
           <t>NODE_S1992_93_0011</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -22610,6 +22664,16 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0014</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0013</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22624,6 +22688,14 @@
         <is>
           <t>NODE_S1992_93_0012</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -22657,6 +22729,8 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22671,6 +22745,14 @@
         <is>
           <t>NODE_S1992_93_0013</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -22704,6 +22786,8 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22718,6 +22802,14 @@
         <is>
           <t>NODE_S1992_93_0014</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -22751,6 +22843,8 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22765,6 +22859,14 @@
         <is>
           <t>NODE_S1992_93_0015</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -22798,6 +22900,8 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22812,6 +22916,14 @@
         <is>
           <t>NODE_S1992_93_0016</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -22845,6 +22957,8 @@
           <t>NODE_S1993_94_0001</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22859,6 +22973,14 @@
         <is>
           <t>NODE_S1992_93_0017</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -22892,6 +23014,8 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22906,6 +23030,14 @@
         <is>
           <t>NODE_S1992_93_0018</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -22939,6 +23071,8 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22953,6 +23087,14 @@
         <is>
           <t>NODE_S1992_93_0019</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -22986,6 +23128,16 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0012</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0011</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23000,6 +23152,14 @@
         <is>
           <t>NODE_S1992_93_0020</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -23117,6 +23277,12 @@
           <t>NODE_S1993_94_0003</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0023</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23126,6 +23292,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -23201,6 +23375,12 @@
           <t>NODE_S1993_94_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23210,6 +23390,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -23243,6 +23431,8 @@
           <t>NODE_S1993_94_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23252,6 +23442,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -23636,6 +23834,8 @@
           <t>NODE_S1993_94_0031</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23645,6 +23845,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -23861,6 +24069,16 @@
           <t>NODE_S1993_94_0037</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0040</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0041</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23875,6 +24093,14 @@
         <is>
           <t>NODE_S1992_93_0060</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -23908,6 +24134,8 @@
           <t>NODE_S1993_94_0037</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23922,6 +24150,14 @@
         <is>
           <t>NODE_S1992_93_0061</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -23955,6 +24191,8 @@
           <t>NODE_S1993_94_0037</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23969,6 +24207,14 @@
         <is>
           <t>NODE_S1992_93_0062</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -24044,6 +24290,16 @@
           <t>NODE_S1993_94_0037</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0040</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0041</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24058,6 +24314,14 @@
         <is>
           <t>NODE_S1992_93_0064</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -24091,6 +24355,8 @@
           <t>NODE_S1993_94_0037</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24105,6 +24371,14 @@
         <is>
           <t>NODE_S1992_93_0065</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -24138,6 +24412,8 @@
           <t>NODE_S1993_94_0037</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24152,6 +24428,14 @@
         <is>
           <t>NODE_S1992_93_0066</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -24907,6 +25191,12 @@
           <t>NODE_S1993_94_0060</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0064</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24921,6 +25211,14 @@
         <is>
           <t>NODE_S1992_93_0084</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -25001,6 +25299,8 @@
           <t>NODE_S1993_94_0060</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25010,6 +25310,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>5.–10. ZČ</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -25305,6 +25613,12 @@
           <t>NODE_S1993_94_0069</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0081</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25314,6 +25628,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -25389,6 +25711,8 @@
           <t>NODE_S1993_94_0069</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25398,6 +25722,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -25755,6 +26087,8 @@
           <t>NODE_S1993_94_0069</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25764,6 +26098,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -25797,6 +26139,8 @@
           <t>NODE_S1993_94_0069</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25806,6 +26150,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -25839,6 +26191,8 @@
           <t>NODE_S1993_94_0069</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25848,6 +26202,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -25881,6 +26243,8 @@
           <t>NODE_S1993_94_0069</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25890,6 +26254,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -26059,6 +26431,12 @@
           <t>NODE_S1993_94_0086</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0090</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26068,6 +26446,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -26143,6 +26529,8 @@
           <t>NODE_S1993_94_0086</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26152,6 +26540,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>-1.–7. ZČ</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -26363,6 +26759,8 @@
           <t>NODE_S1993_94_0086</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26373,7 +26771,17 @@
           <t>complete</t>
         </is>
       </c>
-    </row>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>-1.–7. ZČ</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96"/>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -26473,6 +26881,7 @@
         </is>
       </c>
     </row>
+    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>

--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -1221,6 +1221,11 @@
           <t>HC Olomouc</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F11" t="n">
         <v>44</v>
       </c>
@@ -22729,8 +22734,6 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22786,8 +22789,6 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22843,8 +22844,6 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22900,8 +22899,6 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22957,8 +22954,6 @@
           <t>NODE_S1993_94_0001</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23014,8 +23009,6 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23071,8 +23064,6 @@
           <t>NODE_S1993_94_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23282,7 +23273,6 @@
           <t>NODE_S1993_94_0023</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23380,7 +23370,6 @@
           <t>NODE_S1993_94_0024</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23431,8 +23420,6 @@
           <t>NODE_S1993_94_0003</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23834,8 +23821,6 @@
           <t>NODE_S1993_94_0031</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24134,8 +24119,6 @@
           <t>NODE_S1993_94_0037</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24191,8 +24174,6 @@
           <t>NODE_S1993_94_0037</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24355,8 +24336,6 @@
           <t>NODE_S1993_94_0037</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24412,8 +24391,6 @@
           <t>NODE_S1993_94_0037</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25191,7 +25168,6 @@
           <t>NODE_S1993_94_0060</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>NODE_S1993_94_0064</t>
@@ -25299,8 +25275,6 @@
           <t>NODE_S1993_94_0060</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25613,7 +25587,6 @@
           <t>NODE_S1993_94_0069</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>NODE_S1993_94_0081</t>
@@ -25711,8 +25684,6 @@
           <t>NODE_S1993_94_0069</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26087,8 +26058,6 @@
           <t>NODE_S1993_94_0069</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26139,8 +26108,6 @@
           <t>NODE_S1993_94_0069</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26191,8 +26158,6 @@
           <t>NODE_S1993_94_0069</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26243,8 +26208,6 @@
           <t>NODE_S1993_94_0069</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26431,7 +26394,6 @@
           <t>NODE_S1993_94_0086</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>NODE_S1993_94_0090</t>
@@ -26529,8 +26491,6 @@
           <t>NODE_S1993_94_0086</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26759,8 +26719,6 @@
           <t>NODE_S1993_94_0086</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26780,8 +26738,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -26881,7 +26837,6 @@
         </is>
       </c>
     </row>
-    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
@@ -48689,7 +48644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48905,6 +48860,18 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>V play-off na tři vítězství je 1., 2. a 5. utkání doma; v play-off na dvě vítězství a v baráži je první utkání doma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HC Olomouc</t>
         </is>
       </c>
     </row>

--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -26738,6 +26738,8 @@
         <v>2</v>
       </c>
     </row>
+    <row r="96"/>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -26837,6 +26839,7 @@
         </is>
       </c>
     </row>
+    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>

--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +55,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,6 +117,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -31576,8 +31587,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -31677,7 +31686,6 @@
         </is>
       </c>
     </row>
-    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
@@ -60778,7 +60786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -60835,7 +60843,7 @@
           <t>CLUB_S1993_94_0012</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60855,7 +60863,7 @@
           <t>CLUB_S1993_94_0019</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60875,7 +60883,7 @@
           <t>CLUB_S1993_94_0020</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60895,7 +60903,7 @@
           <t>CLUB_S1993_94_0030</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0066 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -60915,7 +60923,7 @@
           <t>CLUB_S1993_94_0042</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60935,7 +60943,7 @@
           <t>CLUB_S1993_94_0053</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -60955,7 +60963,7 @@
           <t>CLUB_S1993_94_0064</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60975,7 +60983,7 @@
           <t>CLUB_S1993_94_0083</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0161 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -60995,7 +61003,7 @@
           <t>CLUB_S1993_94_0135</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61015,7 +61023,7 @@
           <t>CLUB_S1993_94_0158</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61035,7 +61043,7 @@
           <t>CLUB_S1993_94_0164</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61055,7 +61063,7 @@
           <t>CLUB_S1993_94_0166</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61075,7 +61083,7 @@
           <t>CLUB_S1993_94_0168</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0215 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61095,7 +61103,7 @@
           <t>CLUB_S1993_94_0184</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61115,7 +61123,7 @@
           <t>CLUB_S1993_94_0225</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -61135,7 +61143,7 @@
           <t>CLUB_S1993_94_0227</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -61155,7 +61163,7 @@
           <t>CLUB_S1993_94_0231</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61175,7 +61183,7 @@
           <t>CLUB_S1993_94_0237</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -61195,7 +61203,7 @@
           <t>CLUB_S1993_94_0251</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61215,7 +61223,7 @@
           <t>CLUB_S1993_94_0254</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -61235,7 +61243,7 @@
           <t>CLUB_S1993_94_0282</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -61255,7 +61263,7 @@
           <t>CLUB_S1993_94_0285</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0366 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61275,7 +61283,7 @@
           <t>CLUB_S1993_94_0294</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -61295,7 +61303,7 @@
           <t>CLUB_S1993_94_0307</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61315,7 +61323,7 @@
           <t>CLUB_S1993_94_0310</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -61335,7 +61343,7 @@
           <t>CLUB_S1993_94_0314</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
@@ -61355,7 +61363,7 @@
           <t>CLUB_S1993_94_0361</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0396 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61375,7 +61383,7 @@
           <t>CLUB_S1993_94_0365</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0508 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61395,7 +61403,7 @@
           <t>CLUB_S1993_94_0400</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0475 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61415,11 +61423,37 @@
           <t>CLUB_S1993_94_0404</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1992_93_0476 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Jihomoravský – RP I.třídy (Jihomoravský kraj) · NODE_S1993_94_0100</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Malhostovice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F31"/>

--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -26473,7 +26476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26924,6 +26927,23 @@
         </is>
       </c>
       <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0100</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (Malhostovice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -61443,7 +61463,7 @@
           <t>Jihomoravský – RP I.třídy (Jihomoravský kraj) · NODE_S1993_94_0100</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>máme jen 1 tým (Malhostovice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>

--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -28410,7 +28410,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -28457,7 +28457,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -28499,7 +28499,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -28764,7 +28764,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -28811,7 +28811,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30_Středočeský L50</t>
+          <t>Středočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 RP I.třídy</t>
+          <t>Středočeský, 4. úroveň RP I.třídy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -28900,7 +28900,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 základní část</t>
+          <t>Středočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -28965,7 +28965,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 finále</t>
+          <t>Středočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -29020,7 +29020,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 o udržení</t>
+          <t>Středočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -29075,7 +29075,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 RP II.třídy</t>
+          <t>Středočeský, 4. úroveň RP II.třídy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -29117,7 +29117,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 základní část</t>
+          <t>Středočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -29182,7 +29182,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 finále</t>
+          <t>Středočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -29237,7 +29237,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 o udržení</t>
+          <t>Středočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -29292,7 +29292,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -29339,7 +29339,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50</t>
+          <t>Jihočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -29386,7 +29386,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -29428,7 +29428,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 finálová skupina</t>
+          <t>Jihočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -29470,7 +29470,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 RS</t>
+          <t>Jihočeský, 4. úroveň RS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -29512,7 +29512,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Západočeský L40</t>
+          <t>Západočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -29559,7 +29559,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Západočeský L50</t>
+          <t>Západočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -29606,7 +29606,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 RP I.třídy</t>
+          <t>Západočeský, 4. úroveň RP I.třídy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -29648,7 +29648,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina A</t>
+          <t>Západočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -29695,7 +29695,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina B</t>
+          <t>Západočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -29742,7 +29742,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 finálová skupina</t>
+          <t>Západočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -29784,7 +29784,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 RP II.třídy</t>
+          <t>Západočeský, 4. úroveň RP II.třídy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -29826,7 +29826,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Severočeský L40</t>
+          <t>Severočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -29873,7 +29873,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Severočeský L50</t>
+          <t>Severočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -29920,7 +29920,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -29967,7 +29967,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Východočeský L50</t>
+          <t>Východočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -30014,7 +30014,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 základní část</t>
+          <t>Východočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -30074,7 +30074,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finálová skupina</t>
+          <t>Východočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -30121,7 +30121,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina o záchranu</t>
+          <t>Východočeský, 4. úroveň, skupina o záchranu</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -30171,7 +30171,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 RS</t>
+          <t>Východočeský, 4. úroveň RS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -30213,7 +30213,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina A</t>
+          <t>Východočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -30255,7 +30255,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina B</t>
+          <t>Východočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -30297,7 +30297,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -30344,7 +30344,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50</t>
+          <t>Jihomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -30391,7 +30391,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 RP I.třídy</t>
+          <t>Jihomoravský, 4. úroveň RP I.třídy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -30433,7 +30433,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Základní část</t>
+          <t>Jihomoravský, 4. úroveň, Základní část</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -30488,7 +30488,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finálová skupina</t>
+          <t>Jihomoravský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -30530,7 +30530,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina o umístění</t>
+          <t>Jihomoravský, 4. úroveň, skupina o umístění</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -30580,7 +30580,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 RP II.třídy</t>
+          <t>Jihomoravský, 4. úroveň RP II.třídy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina A</t>
+          <t>Jihomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -30669,7 +30669,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B</t>
+          <t>Jihomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -30716,7 +30716,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina C</t>
+          <t>Jihomoravský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -30763,7 +30763,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina D</t>
+          <t>Jihomoravský, 4. úroveň, skupina D</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -30810,7 +30810,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finálová skupina A+B</t>
+          <t>Jihomoravský, 4. úroveň finálová skupina A+B</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -30857,7 +30857,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finálová skupina C+D</t>
+          <t>Jihomoravský, 4. úroveň finálová skupina C+D</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -30904,7 +30904,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení A</t>
+          <t>Jihomoravský, 4. úroveň o udržení A</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení B</t>
+          <t>Jihomoravský, 4. úroveň o udržení B</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -31004,7 +31004,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení C</t>
+          <t>Jihomoravský, 4. úroveň o udržení C</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -31054,7 +31054,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení D</t>
+          <t>Jihomoravský, 4. úroveň o udržení D</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -31104,7 +31104,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -31151,7 +31151,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50</t>
+          <t>Severomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -31198,7 +31198,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 RP I.třídy</t>
+          <t>Severomoravský, 4. úroveň RP I.třídy</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -31240,7 +31240,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 základní část</t>
+          <t>Severomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -31295,7 +31295,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 finálová skupina</t>
+          <t>Severomoravský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina o udržení</t>
+          <t>Severomoravský, 4. úroveň, skupina o udržení</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -31387,7 +31387,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 RP II.třídy</t>
+          <t>Severomoravský, 4. úroveň RP II.třídy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -31429,7 +31429,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina A</t>
+          <t>Severomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina B</t>
+          <t>Severomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -31523,7 +31523,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 finálová skupina</t>
+          <t>Severomoravský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -31565,7 +31565,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina o udržení</t>
+          <t>Severomoravský, 4. úroveň, skupina o udržení</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -31607,6 +31607,8 @@
         <v>2</v>
       </c>
     </row>
+    <row r="96"/>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -31634,7 +31636,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -31706,6 +31708,7 @@
         </is>
       </c>
     </row>
+    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>

--- a/data/S1993_94_FINAL.xlsx
+++ b/data/S1993_94_FINAL.xlsx
@@ -4145,7 +4145,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -22459,7 +22459,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -22537,7 +22537,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -31607,8 +31607,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -31708,7 +31706,6 @@
         </is>
       </c>
     </row>
-    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
@@ -68213,7 +68210,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
